--- a/output/pdf_financials_xlsx/EMN.xlsx
+++ b/output/pdf_financials_xlsx/EMN.xlsx
@@ -959,22 +959,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3.413356</v>
+        <v>-3.413356</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>6.534075</v>
+        <v>-6.534075</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8.317405000000001</v>
+        <v>-8.317405000000001</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>6.375493</v>
+        <v>-6.375493</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>9.540421</v>
+        <v>-9.540421</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>13.457373</v>
+        <v>-13.457373</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-12.008131</v>
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3.413356</v>
+        <v>-3.413356</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>6.534075</v>
+        <v>-6.534075</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>8.317405000000001</v>
+        <v>-8.317405000000001</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>6.375493</v>
+        <v>-6.375493</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>9.540421</v>
+        <v>-9.540421</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>13.457373</v>
+        <v>-13.457373</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-12.008131</v>
@@ -1233,22 +1233,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3.413356</v>
+        <v>-3.413356</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>6.534075</v>
+        <v>-6.534075</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>8.317405000000001</v>
+        <v>-8.317405000000001</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6.375493</v>
+        <v>-6.375493</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>9.540421</v>
+        <v>-9.540421</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>13.457373</v>
+        <v>-13.457373</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-12.008131</v>
@@ -1335,22 +1335,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>48.762229</v>
+        <v>-48.762229</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>108.90125</v>
+        <v>-108.90125</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>166.3481</v>
+        <v>-166.3481</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>212.516433</v>
+        <v>-212.516433</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>318.014033</v>
+        <v>-318.014033</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>448.5791</v>
+        <v>-448.5791</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>-400.271033</v>
@@ -1369,22 +1369,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3.413356</v>
+        <v>-3.413356</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>6.534075</v>
+        <v>-6.534075</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>8.317405000000001</v>
+        <v>-8.317405000000001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>6.375493</v>
+        <v>-6.375493</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>9.540421</v>
+        <v>-9.540421</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>13.457373</v>
+        <v>-13.457373</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-12.008131</v>
@@ -1437,22 +1437,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3.415457</v>
+        <v>-3.411255</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>6.539731</v>
+        <v>-6.528419</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>8.341078</v>
+        <v>-8.293732</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>6.447421</v>
+        <v>-6.303565</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>9.643796</v>
+        <v>-9.437046</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>13.648502</v>
+        <v>-13.266244</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-11.746958</v>
@@ -1519,22 +1519,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -3639,10 +3639,10 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>10.032</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>10.622</v>
       </c>
     </row>
     <row r="93">
@@ -6336,7 +6336,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -19381,25 +19385,25 @@
         </is>
       </c>
       <c r="E244" s="5" t="n">
-        <v>3.413356</v>
+        <v>-3.413356</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>6.534075</v>
+        <v>-6.534075</v>
       </c>
       <c r="G244" s="5" t="n">
-        <v>8.317405000000001</v>
+        <v>-8.317405000000001</v>
       </c>
       <c r="H244" s="5" t="n">
-        <v>6.375493</v>
+        <v>-6.375493</v>
       </c>
       <c r="I244" s="5" t="n">
-        <v>9.540421</v>
+        <v>-9.540421</v>
       </c>
       <c r="J244" s="5" t="n">
-        <v>13.457373</v>
+        <v>-13.457373</v>
       </c>
       <c r="K244" s="5" t="n">
-        <v>12.008131</v>
+        <v>-12.008131</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EMN.xlsx
+++ b/output/pdf_financials_xlsx/EMN.xlsx
@@ -838,16 +838,16 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.170676</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.635066</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="13">
@@ -1384,16 +1384,16 @@
         <v>-9.540421</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-13.457373</v>
+        <v>-13.286697</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-12.008131</v>
+        <v>-12.643197</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-18.237</v>
+        <v>-18.657</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-17.441</v>
+        <v>-17.602</v>
       </c>
     </row>
     <row r="28">
@@ -1452,16 +1452,16 @@
         <v>-9.437046</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-13.266244</v>
+        <v>-13.095568</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-11.746958</v>
+        <v>-12.382024</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-15.639005</v>
+        <v>-16.059005</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-13.538</v>
+        <v>-13.699</v>
       </c>
     </row>
     <row r="30">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-486.1363071184333</v>
+        <v>-499.1919490208269</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-308.5935719170276</v>
+        <v>-312.2635058126282</v>
       </c>
     </row>
     <row r="31">
@@ -1608,16 +1608,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.860994</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>10.368002</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.084694</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.730739</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>31.218582</v>
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.860994</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>10.368002</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.084694</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.730739</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>31.218582</v>
@@ -2084,16 +2084,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.990222</v>
+        <v>0.129228</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>10.492328</v>
+        <v>0.124326</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.197558</v>
+        <v>0.112864</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.109117</v>
+        <v>0.378378</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.364894</v>
@@ -4700,10 +4700,10 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.276</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.134</v>
       </c>
     </row>
     <row r="125">
@@ -4734,10 +4734,10 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.276</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.134</v>
       </c>
     </row>
     <row r="126">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
@@ -10952,7 +10952,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -16445,7 +16449,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -19206,7 +19210,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">

--- a/output/pdf_financials_xlsx/EMN.xlsx
+++ b/output/pdf_financials_xlsx/EMN.xlsx
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.024319</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>-0.170676</v>
@@ -1381,7 +1381,7 @@
         <v>-6.375493</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-9.540421</v>
+        <v>-9.516102</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-13.286697</v>
@@ -1449,7 +1449,7 @@
         <v>-6.303565</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-9.437046</v>
+        <v>-9.412727</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-13.095568</v>
@@ -4203,16 +4203,16 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.130573</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.09139600000000001</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.060065</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.024162</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -5109,7 +5109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M267"/>
+  <dimension ref="A1:M272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10647,7 +10647,11 @@
           <t>Proceeds from shares issued 9</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -12814,7 +12818,11 @@
           <t>Common shares issued for cash 8</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -14004,7 +14012,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -14535,7 +14547,11 @@
           <t>Accretion expense 7</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -15428,7 +15444,11 @@
           <t>Accretion expense 6</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E177" s="5" t="n">
         <v>0.130573</v>
       </c>
@@ -17629,10 +17649,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I213" s="5" t="n">
+        <v>2.981762</v>
       </c>
       <c r="J213" s="5" t="n">
         <v>2.518262</v>
@@ -17688,10 +17706,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I214" s="5" t="n">
+        <v>0.781625</v>
       </c>
       <c r="J214" s="5" t="n">
         <v>1.584963</v>
@@ -17810,10 +17826,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I216" s="5" t="n">
+        <v>0.013118</v>
       </c>
       <c r="J216" s="5" t="n">
         <v>0.102628</v>
@@ -17873,10 +17887,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I217" s="5" t="n">
+        <v>0.373581</v>
       </c>
       <c r="J217" s="5" t="n">
         <v>0.405365</v>
@@ -17932,10 +17944,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I218" s="5" t="n">
+        <v>0.096009</v>
       </c>
       <c r="J218" s="5" t="n">
         <v>0.221465</v>
@@ -17991,10 +18001,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I219" s="5" t="n">
+        <v>0.033292</v>
       </c>
       <c r="J219" s="5" t="n">
         <v>0.245029</v>
@@ -18050,10 +18058,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I220" s="5" t="n">
+        <v>0.121894</v>
       </c>
       <c r="J220" s="5" t="n">
         <v>0.057173</v>
@@ -18176,10 +18182,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I222" s="5" t="n">
+        <v>4.950474</v>
       </c>
       <c r="J222" s="5" t="n">
         <v>5.671342</v>
@@ -18969,7 +18973,7 @@
         <v>0.091054</v>
       </c>
       <c r="I236" s="5" t="n">
-        <v>0.156877</v>
+        <v>0.181196</v>
       </c>
       <c r="J236" s="5" t="n">
         <v>0.157294</v>
@@ -19233,10 +19237,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I241" s="5" t="n">
+        <v>-0.024319</v>
       </c>
       <c r="J241" s="5" t="n">
         <v>-0.170676</v>
@@ -19491,34 +19493,40 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Project evaluation expenses</t>
+          <t>Chvaletice Project evaluation expenses</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Share-based compensation 8</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
-      <c r="E246" s="5" t="n">
-        <v>1.167653</v>
-      </c>
-      <c r="F246" s="5" t="n">
-        <v>1.854448</v>
-      </c>
-      <c r="G246" s="5" t="n">
-        <v>1.977576</v>
-      </c>
-      <c r="H246" s="5" t="n">
-        <v>1.663702</v>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I246" s="5" t="n">
-        <v>2.981762</v>
-      </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.415733</v>
+      </c>
+      <c r="J246" s="5" t="n">
+        <v>0.488518</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
@@ -19544,12 +19552,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Project evaluation expenses</t>
+          <t>Chvaletice Project evaluation expenses</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Remuneration</t>
+          <t>Drilling, sampling and surveys</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -19558,22 +19566,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F247" s="5" t="n">
-        <v>0.68345</v>
-      </c>
-      <c r="G247" s="5" t="n">
-        <v>1.09827</v>
-      </c>
-      <c r="H247" s="5" t="n">
-        <v>0.943624</v>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I247" s="5" t="n">
-        <v>0.781625</v>
-      </c>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.13346</v>
+      </c>
+      <c r="J247" s="5" t="n">
+        <v>0.001408</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
@@ -19599,34 +19611,40 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Project evaluation expenses</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Share-based compensation 8</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
-      <c r="E248" s="5" t="n">
-        <v>0.07606400000000001</v>
-      </c>
-      <c r="F248" s="5" t="n">
-        <v>0.216043</v>
-      </c>
-      <c r="G248" s="5" t="n">
-        <v>0.254004</v>
-      </c>
-      <c r="H248" s="5" t="n">
-        <v>0.138104</v>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I248" s="5" t="n">
-        <v>0.415733</v>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.417721</v>
+      </c>
+      <c r="J248" s="5" t="n">
+        <v>2.252709</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
@@ -19652,34 +19670,40 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Project evaluation expenses</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Drilling, sampling and surveys</t>
+          <t>- basic and diluted</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
-      <c r="E249" s="5" t="n">
-        <v>0.346025</v>
-      </c>
-      <c r="F249" s="5" t="n">
-        <v>0.329595</v>
-      </c>
-      <c r="G249" s="5" t="n">
-        <v>0.212214</v>
-      </c>
-      <c r="H249" s="5" t="n">
-        <v>0.00369</v>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I249" s="5" t="n">
-        <v>0.13346</v>
-      </c>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>337.294064</v>
+      </c>
+      <c r="J249" s="5" t="n">
+        <v>392.682285</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
@@ -19705,36 +19729,44 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Project evaluation expenses</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Metallurgical</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" s="5" t="n">
-        <v>0.194593</v>
-      </c>
-      <c r="F250" s="5" t="n">
-        <v>0.277209</v>
-      </c>
-      <c r="G250" s="5" t="n">
-        <v>0.380687</v>
-      </c>
-      <c r="H250" s="5" t="n">
-        <v>0.041408</v>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted loss per common share</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I250" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="J250" s="5" t="n">
+        <v>3e-08</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
@@ -19765,28 +19797,24 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" s="5" t="n">
-        <v>0.215955</v>
+        <v>1.167653</v>
       </c>
       <c r="F251" s="5" t="n">
-        <v>0.233241</v>
+        <v>1.854448</v>
       </c>
       <c r="G251" s="5" t="n">
-        <v>0.123338</v>
+        <v>1.977576</v>
       </c>
       <c r="H251" s="5" t="n">
-        <v>0.06378200000000001</v>
+        <v>1.663702</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>0.013118</v>
+        <v>2.981762</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
@@ -19822,28 +19850,26 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Legal and professional fees</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E252" s="5" t="n">
-        <v>0.052385</v>
+          <t>Remuneration</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F252" s="5" t="n">
-        <v>0.459398</v>
+        <v>0.68345</v>
       </c>
       <c r="G252" s="5" t="n">
-        <v>0.370366</v>
+        <v>1.09827</v>
       </c>
       <c r="H252" s="5" t="n">
-        <v>0.154542</v>
+        <v>0.943624</v>
       </c>
       <c r="I252" s="5" t="n">
-        <v>0.373581</v>
+        <v>0.781625</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -19879,24 +19905,24 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Geological</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
       <c r="E253" s="5" t="n">
-        <v>0.096358</v>
+        <v>0.07606400000000001</v>
       </c>
       <c r="F253" s="5" t="n">
-        <v>0.141522</v>
+        <v>0.216043</v>
       </c>
       <c r="G253" s="5" t="n">
-        <v>0.21506</v>
+        <v>0.254004</v>
       </c>
       <c r="H253" s="5" t="n">
-        <v>0.078887</v>
+        <v>0.138104</v>
       </c>
       <c r="I253" s="5" t="n">
-        <v>0.121894</v>
+        <v>0.415733</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -19932,24 +19958,24 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Market studies</t>
+          <t>Drilling, sampling and surveys</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" s="5" t="n">
-        <v>0.028043</v>
+        <v>0.346025</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>0.142961</v>
+        <v>0.329595</v>
       </c>
       <c r="G254" s="5" t="n">
-        <v>0.208681</v>
+        <v>0.212214</v>
       </c>
       <c r="H254" s="5" t="n">
-        <v>0.08304300000000001</v>
+        <v>0.00369</v>
       </c>
       <c r="I254" s="5" t="n">
-        <v>0.096009</v>
+        <v>0.13346</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -19985,24 +20011,26 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Supplies and rentals</t>
+          <t>Metallurgical</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
       <c r="E255" s="5" t="n">
-        <v>0.043196</v>
+        <v>0.194593</v>
       </c>
       <c r="F255" s="5" t="n">
-        <v>0.105176</v>
+        <v>0.277209</v>
       </c>
       <c r="G255" s="5" t="n">
-        <v>0.107019</v>
+        <v>0.380687</v>
       </c>
       <c r="H255" s="5" t="n">
-        <v>0.027179</v>
-      </c>
-      <c r="I255" s="5" t="n">
-        <v>0.033292</v>
+        <v>0.041408</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -20038,28 +20066,28 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Project evaluation expenses total</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E256" s="5" t="n">
-        <v>2.398542</v>
+        <v>0.215955</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>4.589662</v>
+        <v>0.233241</v>
       </c>
       <c r="G256" s="5" t="n">
-        <v>4.947215</v>
+        <v>0.123338</v>
       </c>
       <c r="H256" s="5" t="n">
-        <v>3.197961</v>
+        <v>0.06378200000000001</v>
       </c>
       <c r="I256" s="5" t="n">
-        <v>4.950474</v>
+        <v>0.013118</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -20090,29 +20118,33 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Project evaluation expenses</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
+          <t>Legal and professional fees</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E257" s="5" t="n">
-        <v>0.134753</v>
+        <v>0.052385</v>
       </c>
       <c r="F257" s="5" t="n">
-        <v>0.41482</v>
+        <v>0.459398</v>
       </c>
       <c r="G257" s="5" t="n">
-        <v>0.49363</v>
+        <v>0.370366</v>
       </c>
       <c r="H257" s="5" t="n">
-        <v>0.271707</v>
+        <v>0.154542</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>0.417721</v>
+        <v>0.373581</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -20143,31 +20175,29 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding -</t>
+          <t>Project evaluation expenses</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+          <t>Geological</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E258" s="5" t="n">
+        <v>0.096358</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>116.356568</v>
+        <v>0.141522</v>
       </c>
       <c r="G258" s="5" t="n">
-        <v>172.002914</v>
+        <v>0.21506</v>
       </c>
       <c r="H258" s="5" t="n">
-        <v>190.921092</v>
+        <v>0.078887</v>
       </c>
       <c r="I258" s="5" t="n">
-        <v>337.294064</v>
+        <v>0.121894</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -20198,35 +20228,29 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding -</t>
+          <t>Project evaluation expenses</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Market studies</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" s="5" t="n">
+        <v>0.028043</v>
       </c>
       <c r="F259" s="5" t="n">
-        <v>5.999999999999999e-08</v>
+        <v>0.142961</v>
       </c>
       <c r="G259" s="5" t="n">
-        <v>5e-08</v>
+        <v>0.208681</v>
       </c>
       <c r="H259" s="5" t="n">
-        <v>3e-08</v>
+        <v>0.08304300000000001</v>
       </c>
       <c r="I259" s="5" t="n">
-        <v>3e-08</v>
+        <v>0.096009</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -20262,30 +20286,24 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Project management</t>
+          <t>Supplies and rentals</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
       <c r="E260" s="5" t="n">
-        <v>0.112625</v>
+        <v>0.043196</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>0.146619</v>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.105176</v>
+      </c>
+      <c r="G260" s="5" t="n">
+        <v>0.107019</v>
+      </c>
+      <c r="H260" s="5" t="n">
+        <v>0.027179</v>
+      </c>
+      <c r="I260" s="5" t="n">
+        <v>0.033292</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -20316,35 +20334,33 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Project evaluation expenses</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Filing fees and compliance</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Project evaluation expenses total</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="n">
+        <v>2.398542</v>
       </c>
       <c r="F261" s="5" t="n">
-        <v>0.127142</v>
+        <v>4.589662</v>
       </c>
       <c r="G261" s="5" t="n">
-        <v>0.25871</v>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.947215</v>
+      </c>
+      <c r="H261" s="5" t="n">
+        <v>3.197961</v>
+      </c>
+      <c r="I261" s="5" t="n">
+        <v>4.950474</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -20380,28 +20396,24 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Office rent</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
       <c r="E262" s="5" t="n">
-        <v>0.018</v>
+        <v>0.134753</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>0.028942</v>
+        <v>0.41482</v>
       </c>
       <c r="G262" s="5" t="n">
-        <v>0.053108</v>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.49363</v>
+      </c>
+      <c r="H262" s="5" t="n">
+        <v>0.271707</v>
+      </c>
+      <c r="I262" s="5" t="n">
+        <v>0.417721</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -20432,37 +20444,31 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Project evaluation expenses</t>
+          <t>Weighted average number of common shares outstanding -</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Geophysical</t>
+          <t>Weighted average number of common shares outstanding - basic and diluted</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
-      <c r="E263" s="5" t="n">
-        <v>0.043229</v>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F263" s="5" t="n">
+        <v>116.356568</v>
+      </c>
+      <c r="G263" s="5" t="n">
+        <v>172.002914</v>
+      </c>
+      <c r="H263" s="5" t="n">
+        <v>190.921092</v>
+      </c>
+      <c r="I263" s="5" t="n">
+        <v>337.294064</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -20493,37 +20499,35 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Project evaluation expenses</t>
+          <t>Weighted average number of common shares outstanding -</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Taxes</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" s="5" t="n">
-        <v>0.022416</v>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted loss per common share</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F264" s="5" t="n">
+        <v>5.999999999999999e-08</v>
+      </c>
+      <c r="G264" s="5" t="n">
+        <v>5e-08</v>
+      </c>
+      <c r="H264" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="I264" s="5" t="n">
+        <v>3e-08</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -20554,26 +20558,20 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Project evaluation expenses</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Project management</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" s="5" t="n">
+        <v>0.112625</v>
       </c>
       <c r="F265" s="5" t="n">
-        <v>0.127142</v>
+        <v>0.146619</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -20619,25 +20617,25 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding –</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+          <t>Filing fees and compliance</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
-      <c r="E266" s="5" t="n">
-        <v>48.86492</v>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F266" s="5" t="n">
-        <v>116.356568</v>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.127142</v>
+      </c>
+      <c r="G266" s="5" t="n">
+        <v>0.25871</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -20678,56 +20676,359 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Office rent</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" s="5" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="F267" s="5" t="n">
+        <v>0.028942</v>
+      </c>
+      <c r="G267" s="5" t="n">
+        <v>0.053108</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Project evaluation expenses</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Geophysical</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" s="5" t="n">
+        <v>0.043229</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Project evaluation expenses</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" s="5" t="n">
+        <v>0.022416</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Filing fees</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F270" s="5" t="n">
+        <v>0.127142</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
           <t>Weighted average number of common shares outstanding –</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" s="5" t="n">
+        <v>48.86492</v>
+      </c>
+      <c r="F271" s="5" t="n">
+        <v>116.356568</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding –</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
         <is>
           <t>Basic and diluted loss per common share</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr">
+      <c r="D272" t="inlineStr">
         <is>
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E267" s="5" t="n">
+      <c r="E272" s="5" t="n">
         <v>7e-08</v>
       </c>
-      <c r="F267" s="5" t="n">
+      <c r="F272" s="5" t="n">
         <v>5.999999999999999e-08</v>
       </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M267" t="inlineStr">
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
         <is>
           <t>-</t>
         </is>
